--- a/src/valediction/demo/DEMO - Data Dictionary.xlsx
+++ b/src/valediction/demo/DEMO - Data Dictionary.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\davisci\Offline\Bitbucket\Kitchen Projects\SDE API\src\bc_platforms\demo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\davisci\Offline\Coding\Kitchen\valediction\src\valediction\demo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E639CE57-02A0-4B5C-BB94-07689B27F7AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18CDFB3B-DE46-4AF0-90BA-EBF800192DFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-75" yWindow="-16410" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{2525A127-7ECE-4F76-8B09-5FB1513E16D9}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{2525A127-7ECE-4F76-8B09-5FB1513E16D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Details" sheetId="5" r:id="rId1"/>
@@ -389,9 +389,6 @@
     <t>Organisation(s)</t>
   </si>
   <si>
-    <t>v1.0</t>
-  </si>
-  <si>
     <t>Project Details</t>
   </si>
   <si>
@@ -404,9 +401,6 @@
     <t>Version</t>
   </si>
   <si>
-    <t>Datetime</t>
-  </si>
-  <si>
     <t>Datetime (including time)</t>
   </si>
   <si>
@@ -588,6 +582,12 @@
   </si>
   <si>
     <t>+</t>
+  </si>
+  <si>
+    <t>Timestamp</t>
+  </si>
+  <si>
+    <t>v1.1</t>
   </si>
 </sst>
 </file>
@@ -876,6 +876,19 @@
   </cellStyles>
   <dxfs count="21">
     <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <i/>
@@ -980,19 +993,6 @@
       </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1077,7 +1077,7 @@
     <tableColumn id="5" xr3:uid="{F9687416-C526-4DCC-BAD0-4C1269CDA50C}" name="Primary Key" dataDxfId="16"/>
     <tableColumn id="12" xr3:uid="{06D4DABA-C917-4B23-A286-2823FE56344C}" name="Foreign Key Target" dataDxfId="15"/>
     <tableColumn id="3" xr3:uid="{5479EABB-FBDA-4C2E-8FCB-DD8FE6159120}" name="Column Description"/>
-    <tableColumn id="7" xr3:uid="{A60A11A9-7EC4-4138-8607-7B950D3A810E}" name="CHECKS" dataDxfId="14">
+    <tableColumn id="7" xr3:uid="{A60A11A9-7EC4-4138-8607-7B950D3A810E}" name="CHECKS" dataDxfId="0">
       <calculatedColumnFormula array="1">IF(
   COUNTA(Columns[[#This Row],[Table]:[Column Description]])=0,"",
   IF(
@@ -1120,7 +1120,7 @@
                                 LOWER(TRIM(Columns[[#This Row],[Data Type]]))="text",
                                 LOWER(TRIM(Columns[[#This Row],[Data Type]]))="integer",
                                 LOWER(TRIM(Columns[[#This Row],[Data Type]]))="date",
-                                LOWER(TRIM(Columns[[#This Row],[Data Type]]))="datetime"
+                                LOWER(TRIM(Columns[[#This Row],[Data Type]]))="timestamp"
                               ))
                           ),
                           "Error: Invalid Data Type for Primary Key",
@@ -1158,7 +1158,7 @@
     <tableColumn id="3" xr3:uid="{22D247A6-1836-420A-81C2-8FD61D2D49E1}" name="Code"/>
     <tableColumn id="4" xr3:uid="{A334EAE4-5837-471A-9689-C87A2CC6D3BE}" name="Name"/>
     <tableColumn id="6" xr3:uid="{11C456F2-064F-43E6-BF85-222C7E79D7C0}" name="Additional Description"/>
-    <tableColumn id="5" xr3:uid="{9954DEBD-DF72-4F68-852C-139D20526AAC}" name="CHECKS" dataDxfId="13">
+    <tableColumn id="5" xr3:uid="{9954DEBD-DF72-4F68-852C-139D20526AAC}" name="CHECKS" dataDxfId="14">
       <calculatedColumnFormula array="1">IF(
   COUNTA(Enumerations[[#This Row],[Table]:[Name]])=0,"",
   IF(
@@ -1502,7 +1502,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="29" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B1" s="29"/>
     </row>
@@ -1511,7 +1511,7 @@
         <v>22</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -1526,24 +1526,24 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="30" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B5" s="30"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -1552,24 +1552,24 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="32" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B9" s="32"/>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -1578,21 +1578,21 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="31" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B13" s="31"/>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="19" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B14" s="21" t="s">
-        <v>25</v>
+        <v>91</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="20" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B15" s="22" cm="1">
         <f t="array" ref="B15">_xlfn.LET(
@@ -1604,7 +1604,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B16" s="23" cm="1">
         <f t="array" ref="B16">_xlfn.LET(
@@ -1616,7 +1616,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="20" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B17" s="24" t="str">
         <f ca="1">IF(
@@ -1692,10 +1692,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B2" s="25" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C2" s="1" t="str" cm="1">
         <f t="array" aca="1" ref="C2" ca="1">IF(Tables[[#This Row],[Table]]="","",
@@ -1719,10 +1719,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="25" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B3" s="25" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C3" s="26" t="str" cm="1">
         <f t="array" aca="1" ref="C3" ca="1">IF(Tables[[#This Row],[Table]]="","",
@@ -1746,10 +1746,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="25" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B4" s="25" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C4" s="26" t="str" cm="1">
         <f t="array" aca="1" ref="C4" ca="1">IF(Tables[[#This Row],[Table]]="","",
@@ -1773,10 +1773,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="25" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B5" s="25" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C5" s="26" t="str" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">IF(Tables[[#This Row],[Table]]="","",
@@ -1800,7 +1800,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:C5">
-    <cfRule type="expression" dxfId="12" priority="1">
+    <cfRule type="expression" dxfId="13" priority="1">
       <formula>LEFT($C2,5)="Error"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1864,7 +1864,7 @@
         <v>20</v>
       </c>
       <c r="I1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J1" t="s">
         <v>16</v>
@@ -1875,10 +1875,10 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -1938,7 +1938,7 @@
                                 LOWER(TRIM(Columns[[#This Row],[Data Type]]))="text",
                                 LOWER(TRIM(Columns[[#This Row],[Data Type]]))="integer",
                                 LOWER(TRIM(Columns[[#This Row],[Data Type]]))="date",
-                                LOWER(TRIM(Columns[[#This Row],[Data Type]]))="datetime"
+                                LOWER(TRIM(Columns[[#This Row],[Data Type]]))="timestamp"
                               ))
                           ),
                           "Error: Invalid Data Type for Primary Key",
@@ -1966,10 +1966,10 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -2023,7 +2023,7 @@
                                 LOWER(TRIM(Columns[[#This Row],[Data Type]]))="text",
                                 LOWER(TRIM(Columns[[#This Row],[Data Type]]))="integer",
                                 LOWER(TRIM(Columns[[#This Row],[Data Type]]))="date",
-                                LOWER(TRIM(Columns[[#This Row],[Data Type]]))="datetime"
+                                LOWER(TRIM(Columns[[#This Row],[Data Type]]))="timestamp"
                               ))
                           ),
                           "Error: Invalid Data Type for Primary Key",
@@ -2051,10 +2051,10 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -2111,7 +2111,7 @@
                                 LOWER(TRIM(Columns[[#This Row],[Data Type]]))="text",
                                 LOWER(TRIM(Columns[[#This Row],[Data Type]]))="integer",
                                 LOWER(TRIM(Columns[[#This Row],[Data Type]]))="date",
-                                LOWER(TRIM(Columns[[#This Row],[Data Type]]))="datetime"
+                                LOWER(TRIM(Columns[[#This Row],[Data Type]]))="timestamp"
                               ))
                           ),
                           "Error: Invalid Data Type for Primary Key",
@@ -2139,10 +2139,10 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -2199,7 +2199,7 @@
                                 LOWER(TRIM(Columns[[#This Row],[Data Type]]))="text",
                                 LOWER(TRIM(Columns[[#This Row],[Data Type]]))="integer",
                                 LOWER(TRIM(Columns[[#This Row],[Data Type]]))="date",
-                                LOWER(TRIM(Columns[[#This Row],[Data Type]]))="datetime"
+                                LOWER(TRIM(Columns[[#This Row],[Data Type]]))="timestamp"
                               ))
                           ),
                           "Error: Invalid Data Type for Primary Key",
@@ -2227,10 +2227,10 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C6">
         <v>5</v>
@@ -2284,7 +2284,7 @@
                                 LOWER(TRIM(Columns[[#This Row],[Data Type]]))="text",
                                 LOWER(TRIM(Columns[[#This Row],[Data Type]]))="integer",
                                 LOWER(TRIM(Columns[[#This Row],[Data Type]]))="date",
-                                LOWER(TRIM(Columns[[#This Row],[Data Type]]))="datetime"
+                                LOWER(TRIM(Columns[[#This Row],[Data Type]]))="timestamp"
                               ))
                           ),
                           "Error: Invalid Data Type for Primary Key",
@@ -2312,10 +2312,10 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B7" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -2331,7 +2331,7 @@
         <v>1</v>
       </c>
       <c r="I7" s="13" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="K7" s="26" t="str" cm="1">
         <f t="array" aca="1" ref="K7" ca="1">IF(
@@ -2376,7 +2376,7 @@
                                 LOWER(TRIM(Columns[[#This Row],[Data Type]]))="text",
                                 LOWER(TRIM(Columns[[#This Row],[Data Type]]))="integer",
                                 LOWER(TRIM(Columns[[#This Row],[Data Type]]))="date",
-                                LOWER(TRIM(Columns[[#This Row],[Data Type]]))="datetime"
+                                LOWER(TRIM(Columns[[#This Row],[Data Type]]))="timestamp"
                               ))
                           ),
                           "Error: Invalid Data Type for Primary Key",
@@ -2404,10 +2404,10 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B8" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C8">
         <v>2</v>
@@ -2463,7 +2463,7 @@
                                 LOWER(TRIM(Columns[[#This Row],[Data Type]]))="text",
                                 LOWER(TRIM(Columns[[#This Row],[Data Type]]))="integer",
                                 LOWER(TRIM(Columns[[#This Row],[Data Type]]))="date",
-                                LOWER(TRIM(Columns[[#This Row],[Data Type]]))="datetime"
+                                LOWER(TRIM(Columns[[#This Row],[Data Type]]))="timestamp"
                               ))
                           ),
                           "Error: Invalid Data Type for Primary Key",
@@ -2491,10 +2491,10 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B9" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C9">
         <v>3</v>
@@ -2553,7 +2553,7 @@
                                 LOWER(TRIM(Columns[[#This Row],[Data Type]]))="text",
                                 LOWER(TRIM(Columns[[#This Row],[Data Type]]))="integer",
                                 LOWER(TRIM(Columns[[#This Row],[Data Type]]))="date",
-                                LOWER(TRIM(Columns[[#This Row],[Data Type]]))="datetime"
+                                LOWER(TRIM(Columns[[#This Row],[Data Type]]))="timestamp"
                               ))
                           ),
                           "Error: Invalid Data Type for Primary Key",
@@ -2581,10 +2581,10 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B10" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C10">
         <v>4</v>
@@ -2596,7 +2596,7 @@
         <v>1</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H10" s="28"/>
       <c r="I10" s="13"/>
@@ -2643,7 +2643,7 @@
                                 LOWER(TRIM(Columns[[#This Row],[Data Type]]))="text",
                                 LOWER(TRIM(Columns[[#This Row],[Data Type]]))="integer",
                                 LOWER(TRIM(Columns[[#This Row],[Data Type]]))="date",
-                                LOWER(TRIM(Columns[[#This Row],[Data Type]]))="datetime"
+                                LOWER(TRIM(Columns[[#This Row],[Data Type]]))="timestamp"
                               ))
                           ),
                           "Error: Invalid Data Type for Primary Key",
@@ -2671,10 +2671,10 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B11" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -2690,7 +2690,7 @@
         <v>1</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="K11" s="26" t="str" cm="1">
         <f t="array" aca="1" ref="K11" ca="1">IF(
@@ -2735,7 +2735,7 @@
                                 LOWER(TRIM(Columns[[#This Row],[Data Type]]))="text",
                                 LOWER(TRIM(Columns[[#This Row],[Data Type]]))="integer",
                                 LOWER(TRIM(Columns[[#This Row],[Data Type]]))="date",
-                                LOWER(TRIM(Columns[[#This Row],[Data Type]]))="datetime"
+                                LOWER(TRIM(Columns[[#This Row],[Data Type]]))="timestamp"
                               ))
                           ),
                           "Error: Invalid Data Type for Primary Key",
@@ -2763,10 +2763,10 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B12" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C12">
         <v>2</v>
@@ -2822,7 +2822,7 @@
                                 LOWER(TRIM(Columns[[#This Row],[Data Type]]))="text",
                                 LOWER(TRIM(Columns[[#This Row],[Data Type]]))="integer",
                                 LOWER(TRIM(Columns[[#This Row],[Data Type]]))="date",
-                                LOWER(TRIM(Columns[[#This Row],[Data Type]]))="datetime"
+                                LOWER(TRIM(Columns[[#This Row],[Data Type]]))="timestamp"
                               ))
                           ),
                           "Error: Invalid Data Type for Primary Key",
@@ -2850,10 +2850,10 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B13" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C13">
         <v>3</v>
@@ -2909,7 +2909,7 @@
                                 LOWER(TRIM(Columns[[#This Row],[Data Type]]))="text",
                                 LOWER(TRIM(Columns[[#This Row],[Data Type]]))="integer",
                                 LOWER(TRIM(Columns[[#This Row],[Data Type]]))="date",
-                                LOWER(TRIM(Columns[[#This Row],[Data Type]]))="datetime"
+                                LOWER(TRIM(Columns[[#This Row],[Data Type]]))="timestamp"
                               ))
                           ),
                           "Error: Invalid Data Type for Primary Key",
@@ -2937,10 +2937,10 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B14" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C14">
         <v>4</v>
@@ -2997,7 +2997,7 @@
                                 LOWER(TRIM(Columns[[#This Row],[Data Type]]))="text",
                                 LOWER(TRIM(Columns[[#This Row],[Data Type]]))="integer",
                                 LOWER(TRIM(Columns[[#This Row],[Data Type]]))="date",
-                                LOWER(TRIM(Columns[[#This Row],[Data Type]]))="datetime"
+                                LOWER(TRIM(Columns[[#This Row],[Data Type]]))="timestamp"
                               ))
                           ),
                           "Error: Invalid Data Type for Primary Key",
@@ -3025,10 +3025,10 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B15" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C15">
         <v>5</v>
@@ -3087,7 +3087,7 @@
                                 LOWER(TRIM(Columns[[#This Row],[Data Type]]))="text",
                                 LOWER(TRIM(Columns[[#This Row],[Data Type]]))="integer",
                                 LOWER(TRIM(Columns[[#This Row],[Data Type]]))="date",
-                                LOWER(TRIM(Columns[[#This Row],[Data Type]]))="datetime"
+                                LOWER(TRIM(Columns[[#This Row],[Data Type]]))="timestamp"
                               ))
                           ),
                           "Error: Invalid Data Type for Primary Key",
@@ -3115,10 +3115,10 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B16" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C16">
         <v>6</v>
@@ -3175,7 +3175,7 @@
                                 LOWER(TRIM(Columns[[#This Row],[Data Type]]))="text",
                                 LOWER(TRIM(Columns[[#This Row],[Data Type]]))="integer",
                                 LOWER(TRIM(Columns[[#This Row],[Data Type]]))="date",
-                                LOWER(TRIM(Columns[[#This Row],[Data Type]]))="datetime"
+                                LOWER(TRIM(Columns[[#This Row],[Data Type]]))="timestamp"
                               ))
                           ),
                           "Error: Invalid Data Type for Primary Key",
@@ -3203,10 +3203,10 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B17" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C17">
         <v>7</v>
@@ -3263,7 +3263,7 @@
                                 LOWER(TRIM(Columns[[#This Row],[Data Type]]))="text",
                                 LOWER(TRIM(Columns[[#This Row],[Data Type]]))="integer",
                                 LOWER(TRIM(Columns[[#This Row],[Data Type]]))="date",
-                                LOWER(TRIM(Columns[[#This Row],[Data Type]]))="datetime"
+                                LOWER(TRIM(Columns[[#This Row],[Data Type]]))="timestamp"
                               ))
                           ),
                           "Error: Invalid Data Type for Primary Key",
@@ -3291,10 +3291,10 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B18" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C18">
         <v>8</v>
@@ -3348,7 +3348,7 @@
                                 LOWER(TRIM(Columns[[#This Row],[Data Type]]))="text",
                                 LOWER(TRIM(Columns[[#This Row],[Data Type]]))="integer",
                                 LOWER(TRIM(Columns[[#This Row],[Data Type]]))="date",
-                                LOWER(TRIM(Columns[[#This Row],[Data Type]]))="datetime"
+                                LOWER(TRIM(Columns[[#This Row],[Data Type]]))="timestamp"
                               ))
                           ),
                           "Error: Invalid Data Type for Primary Key",
@@ -3376,10 +3376,10 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B19" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C19">
         <v>9</v>
@@ -3391,7 +3391,7 @@
         <v>8</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H19" s="28"/>
       <c r="I19" s="13"/>
@@ -3438,7 +3438,7 @@
                                 LOWER(TRIM(Columns[[#This Row],[Data Type]]))="text",
                                 LOWER(TRIM(Columns[[#This Row],[Data Type]]))="integer",
                                 LOWER(TRIM(Columns[[#This Row],[Data Type]]))="date",
-                                LOWER(TRIM(Columns[[#This Row],[Data Type]]))="datetime"
+                                LOWER(TRIM(Columns[[#This Row],[Data Type]]))="timestamp"
                               ))
                           ),
                           "Error: Invalid Data Type for Primary Key",
@@ -3466,10 +3466,10 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B20" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C20">
         <v>10</v>
@@ -3481,7 +3481,7 @@
         <v>1</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H20" s="28"/>
       <c r="I20" s="13"/>
@@ -3528,7 +3528,7 @@
                                 LOWER(TRIM(Columns[[#This Row],[Data Type]]))="text",
                                 LOWER(TRIM(Columns[[#This Row],[Data Type]]))="integer",
                                 LOWER(TRIM(Columns[[#This Row],[Data Type]]))="date",
-                                LOWER(TRIM(Columns[[#This Row],[Data Type]]))="datetime"
+                                LOWER(TRIM(Columns[[#This Row],[Data Type]]))="timestamp"
                               ))
                           ),
                           "Error: Invalid Data Type for Primary Key",
@@ -3556,10 +3556,10 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B21" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C21">
         <v>11</v>
@@ -3613,7 +3613,7 @@
                                 LOWER(TRIM(Columns[[#This Row],[Data Type]]))="text",
                                 LOWER(TRIM(Columns[[#This Row],[Data Type]]))="integer",
                                 LOWER(TRIM(Columns[[#This Row],[Data Type]]))="date",
-                                LOWER(TRIM(Columns[[#This Row],[Data Type]]))="datetime"
+                                LOWER(TRIM(Columns[[#This Row],[Data Type]]))="timestamp"
                               ))
                           ),
                           "Error: Invalid Data Type for Primary Key",
@@ -3641,10 +3641,10 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B22" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C22">
         <v>12</v>
@@ -3698,7 +3698,7 @@
                                 LOWER(TRIM(Columns[[#This Row],[Data Type]]))="text",
                                 LOWER(TRIM(Columns[[#This Row],[Data Type]]))="integer",
                                 LOWER(TRIM(Columns[[#This Row],[Data Type]]))="date",
-                                LOWER(TRIM(Columns[[#This Row],[Data Type]]))="datetime"
+                                LOWER(TRIM(Columns[[#This Row],[Data Type]]))="timestamp"
                               ))
                           ),
                           "Error: Invalid Data Type for Primary Key",
@@ -3726,10 +3726,10 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B23" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C23">
         <v>1</v>
@@ -3745,7 +3745,7 @@
         <v>1</v>
       </c>
       <c r="I23" s="13" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="K23" s="26" t="str" cm="1">
         <f t="array" aca="1" ref="K23" ca="1">IF(
@@ -3790,7 +3790,7 @@
                                 LOWER(TRIM(Columns[[#This Row],[Data Type]]))="text",
                                 LOWER(TRIM(Columns[[#This Row],[Data Type]]))="integer",
                                 LOWER(TRIM(Columns[[#This Row],[Data Type]]))="date",
-                                LOWER(TRIM(Columns[[#This Row],[Data Type]]))="datetime"
+                                LOWER(TRIM(Columns[[#This Row],[Data Type]]))="timestamp"
                               ))
                           ),
                           "Error: Invalid Data Type for Primary Key",
@@ -3818,16 +3818,16 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B24" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C24">
         <v>2</v>
       </c>
       <c r="D24" t="s">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="G24" s="2"/>
       <c r="H24" s="28">
@@ -3877,7 +3877,7 @@
                                 LOWER(TRIM(Columns[[#This Row],[Data Type]]))="text",
                                 LOWER(TRIM(Columns[[#This Row],[Data Type]]))="integer",
                                 LOWER(TRIM(Columns[[#This Row],[Data Type]]))="date",
-                                LOWER(TRIM(Columns[[#This Row],[Data Type]]))="datetime"
+                                LOWER(TRIM(Columns[[#This Row],[Data Type]]))="timestamp"
                               ))
                           ),
                           "Error: Invalid Data Type for Primary Key",
@@ -3905,10 +3905,10 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>83</v>
+      </c>
+      <c r="B25" t="s">
         <v>85</v>
-      </c>
-      <c r="B25" t="s">
-        <v>87</v>
       </c>
       <c r="C25">
         <v>3</v>
@@ -3967,7 +3967,7 @@
                                 LOWER(TRIM(Columns[[#This Row],[Data Type]]))="text",
                                 LOWER(TRIM(Columns[[#This Row],[Data Type]]))="integer",
                                 LOWER(TRIM(Columns[[#This Row],[Data Type]]))="date",
-                                LOWER(TRIM(Columns[[#This Row],[Data Type]]))="datetime"
+                                LOWER(TRIM(Columns[[#This Row],[Data Type]]))="timestamp"
                               ))
                           ),
                           "Error: Invalid Data Type for Primary Key",
@@ -3995,10 +3995,10 @@
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B26" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C26">
         <v>4</v>
@@ -4052,7 +4052,7 @@
                                 LOWER(TRIM(Columns[[#This Row],[Data Type]]))="text",
                                 LOWER(TRIM(Columns[[#This Row],[Data Type]]))="integer",
                                 LOWER(TRIM(Columns[[#This Row],[Data Type]]))="date",
-                                LOWER(TRIM(Columns[[#This Row],[Data Type]]))="datetime"
+                                LOWER(TRIM(Columns[[#This Row],[Data Type]]))="timestamp"
                               ))
                           ),
                           "Error: Invalid Data Type for Primary Key",
@@ -4080,18 +4080,18 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A24:A26">
-    <cfRule type="expression" dxfId="11" priority="1">
+    <cfRule type="expression" dxfId="12" priority="1">
       <formula>$K24="Incomplete"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="2">
+    <cfRule type="expression" dxfId="11" priority="2">
       <formula>LEFT($K24,5)="Error"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:K26">
-    <cfRule type="expression" dxfId="9" priority="6">
+    <cfRule type="expression" dxfId="10" priority="6">
       <formula>$K2="Incomplete"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="7">
+    <cfRule type="expression" dxfId="9" priority="7">
       <formula>LEFT($K2,5)="Error"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4163,16 +4163,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D2" t="s">
         <v>61</v>
-      </c>
-      <c r="D2" t="s">
-        <v>63</v>
       </c>
       <c r="F2" s="1" t="str" cm="1">
         <f t="array" ref="F2">IF(
@@ -4200,16 +4200,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C3" t="s">
         <v>60</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>62</v>
-      </c>
-      <c r="D3" t="s">
-        <v>64</v>
       </c>
       <c r="F3" s="26" t="str" cm="1">
         <f t="array" ref="F3">IF(
@@ -4237,19 +4237,19 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C4" t="s">
+        <v>78</v>
+      </c>
+      <c r="D4" t="s">
         <v>80</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>82</v>
-      </c>
-      <c r="E4" t="s">
-        <v>84</v>
       </c>
       <c r="F4" s="26" t="str" cm="1">
         <f t="array" ref="F4">IF(
@@ -4277,19 +4277,19 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C5" t="s">
+        <v>79</v>
+      </c>
+      <c r="D5" t="s">
         <v>81</v>
       </c>
-      <c r="D5" t="s">
-        <v>83</v>
-      </c>
       <c r="E5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F5" s="26" t="str" cm="1">
         <f t="array" ref="F5">IF(
@@ -4317,19 +4317,19 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B6" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C6" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F6" s="26" t="str" cm="1">
         <f t="array" ref="F6">IF(
@@ -4357,19 +4357,19 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B7" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E7" t="s">
         <v>77</v>
-      </c>
-      <c r="E7" t="s">
-        <v>79</v>
       </c>
       <c r="F7" s="26" t="str" cm="1">
         <f t="array" ref="F7">IF(
@@ -4397,34 +4397,34 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A3:B3">
-    <cfRule type="expression" dxfId="7" priority="7">
+    <cfRule type="expression" dxfId="8" priority="7">
       <formula>$F3="Incomplete"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="8">
+    <cfRule type="expression" dxfId="7" priority="8">
       <formula>LEFT($F3,5)="Error"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A4:B7">
-    <cfRule type="expression" dxfId="5" priority="3">
+    <cfRule type="expression" dxfId="6" priority="3">
       <formula>$K4="Incomplete"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="4">
+    <cfRule type="expression" dxfId="5" priority="4">
       <formula>LEFT($K4,5)="Error"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:F7">
-    <cfRule type="expression" dxfId="3" priority="9">
+    <cfRule type="expression" dxfId="4" priority="9">
       <formula>$F2="Incomplete"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="10">
+    <cfRule type="expression" dxfId="3" priority="10">
       <formula>LEFT($F2,5)="Error"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B5">
-    <cfRule type="expression" dxfId="1" priority="1">
+    <cfRule type="expression" dxfId="2" priority="1">
       <formula>$K5="Incomplete"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="2">
+    <cfRule type="expression" dxfId="1" priority="2">
       <formula>LEFT($K5,5)="Error"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4503,10 +4503,10 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="B6" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -4526,27 +4526,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Comments xmlns="e9944761-107d-482c-b0ee-b6577fad07ab" xsi:nil="true"/>
-    <TaxCatchAll xmlns="6b33fda9-98b8-43a9-8947-77f58065d3a5" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e9944761-107d-482c-b0ee-b6577fad07ab">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101007B0CC668BF08D640A1205605FD4980F1" ma:contentTypeVersion="20" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="e62c799f916d10c9eb1fb84c4b8acd8b">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="6b33fda9-98b8-43a9-8947-77f58065d3a5" xmlns:ns3="e9944761-107d-482c-b0ee-b6577fad07ab" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="48efd8e6e2cb24b246535df6e56ba147" ns2:_="" ns3:_="">
     <xsd:import namespace="6b33fda9-98b8-43a9-8947-77f58065d3a5"/>
@@ -4809,10 +4788,42 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Comments xmlns="e9944761-107d-482c-b0ee-b6577fad07ab" xsi:nil="true"/>
+    <TaxCatchAll xmlns="6b33fda9-98b8-43a9-8947-77f58065d3a5" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e9944761-107d-482c-b0ee-b6577fad07ab">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ACE91027-FAB8-48AE-BC46-EBA6BA66B56B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{267B93DB-3ECE-472E-8157-C8F47EB5A525}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="6b33fda9-98b8-43a9-8947-77f58065d3a5"/>
+    <ds:schemaRef ds:uri="e9944761-107d-482c-b0ee-b6577fad07ab"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -4829,20 +4840,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{267B93DB-3ECE-472E-8157-C8F47EB5A525}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ACE91027-FAB8-48AE-BC46-EBA6BA66B56B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="6b33fda9-98b8-43a9-8947-77f58065d3a5"/>
-    <ds:schemaRef ds:uri="e9944761-107d-482c-b0ee-b6577fad07ab"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>